--- a/mapping/impix/S2_매핑정의서_IMPIX.xlsx
+++ b/mapping/impix/S2_매핑정의서_IMPIX.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 15:00 · tools/automap · 계획 mapping/impix/s2_plan.yaml</t>
+          <t>2026-10-23 15:02 · tools/automap · 계획 mapping/impix/s2_plan.yaml</t>
         </is>
       </c>
     </row>

--- a/mapping/impix/S2_매핑정의서_IMPIX.xlsx
+++ b/mapping/impix/S2_매핑정의서_IMPIX.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구조매핑" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="속성매핑" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="컬럼판정" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="후보(미해소)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="코드대응" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="단위대응" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="식별대응" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="테이블판정" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검사" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="승인" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="요약" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="구조매핑" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="속성매핑" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="컬럼판정" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="후보(미해소)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="코드대응" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="단위대응" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="식별대응" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="테이블판정" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="검사" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="승인" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요약'!$A$1:$B$15</definedName>
@@ -546,7 +546,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 15:02 · tools/automap · 계획 mapping/impix/s2_plan.yaml</t>
+          <t>2026-10-23 17:20 · tools/automap · 계획 mapping/impix/s2_plan.yaml</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>298 (71.6%) — 목표 70% 이상</t>
+          <t>299 (71.9%) — 목표 70% 이상</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
@@ -979,7 +979,7 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/Enterprise.yaml</t>
+          <t>mapping\impix\erp\Enterprise.yaml</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/Site.yaml</t>
+          <t>mapping\impix\erp\Site.yaml</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr"/>
@@ -1066,7 +1066,11 @@
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>use_yn = 'Y'</t>
+        </is>
+      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
           <t>EnterpriseID=xref(enterprise, comp_cd), SiteID=xref(site, bizarea_cd), PlantID=xref(plant, plant_cd)</t>
@@ -1083,7 +1087,7 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/Plant.yaml</t>
+          <t>mapping\impix\erp\Plant.yaml</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr"/>
@@ -1118,7 +1122,11 @@
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>use_yn = 'Y'</t>
+        </is>
+      </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
           <t>EnterpriseID=const(IMPIX), SiteID=const(HQ), PlantID=xref(plant, plant_cd)</t>
@@ -1135,7 +1143,7 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/Department.yaml</t>
+          <t>mapping\impix\erp\Department.yaml</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr"/>
@@ -1187,7 +1195,7 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/Personnel.yaml</t>
+          <t>mapping\impix\erp\Personnel.yaml</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr"/>
@@ -1243,7 +1251,7 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/ItemMaster.yaml</t>
+          <t>mapping\impix\erp\ItemMaster.yaml</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
@@ -1295,7 +1303,7 @@
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/BOMHeader.yaml</t>
+          <t>mapping\impix\erp\BOMHeader.yaml</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
@@ -1351,7 +1359,7 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/BOMLine.yaml</t>
+          <t>mapping\impix\erp\BOMLine.yaml</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr"/>
@@ -1403,7 +1411,7 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/RoutingHeader.yaml</t>
+          <t>mapping\impix\erp\RoutingHeader.yaml</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr"/>
@@ -1459,7 +1467,7 @@
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/RoutingLine.yaml</t>
+          <t>mapping\impix\erp\RoutingLine.yaml</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr"/>
@@ -1515,7 +1523,7 @@
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/mes/Operation.yaml</t>
+          <t>mapping\impix\mes\Operation.yaml</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr"/>
@@ -1567,7 +1575,7 @@
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/Line.yaml</t>
+          <t>mapping\impix\erp\Line.yaml</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
@@ -1619,7 +1627,7 @@
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/WarehouseLocationHeader.yaml</t>
+          <t>mapping\impix\erp\WarehouseLocationHeader.yaml</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr"/>
@@ -1671,7 +1679,7 @@
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/mes/Equipment.yaml</t>
+          <t>mapping\impix\mes\Equipment.yaml</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
@@ -1723,7 +1731,7 @@
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/mes/OperationEquipment.yaml</t>
+          <t>mapping\impix\mes\OperationEquipment.yaml</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr"/>
@@ -1775,7 +1783,7 @@
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/CustomerPartyMaster.yaml</t>
+          <t>mapping\impix\erp\CustomerPartyMaster.yaml</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr"/>
@@ -1827,7 +1835,7 @@
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/VendorPartyMaster.yaml</t>
+          <t>mapping\impix\erp\VendorPartyMaster.yaml</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr"/>
@@ -1883,7 +1891,7 @@
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/BasePrice.yaml</t>
+          <t>mapping\impix\erp\BasePrice.yaml</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr"/>
@@ -1939,7 +1947,7 @@
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/StandardCost.yaml</t>
+          <t>mapping\impix\erp\StandardCost.yaml</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
@@ -1978,7 +1986,11 @@
           <t>mes.tm_eqp ON eqp_id = e.eqp_id</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>use_flag = 'Y'</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
           <t>EnterpriseID=const(IMPIX), SiteID=const(HQ), PlantID=xref(plant, e.fac_id)</t>
@@ -1995,7 +2007,7 @@
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/mes/EquipmentParameter.yaml</t>
+          <t>mapping\impix\mes\EquipmentParameter.yaml</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr"/>
@@ -2047,7 +2059,7 @@
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/SalesPlan.yaml</t>
+          <t>mapping\impix\erp\SalesPlan.yaml</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr"/>
@@ -2099,7 +2111,7 @@
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/SalesOrderHeader.yaml</t>
+          <t>mapping\impix\erp\SalesOrderHeader.yaml</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
@@ -2151,7 +2163,7 @@
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/SalesOrderLine.yaml</t>
+          <t>mapping\impix\erp\SalesOrderLine.yaml</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr"/>
@@ -2203,7 +2215,7 @@
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/ProductRelease.yaml</t>
+          <t>mapping\impix\erp\ProductRelease.yaml</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr"/>
@@ -2255,7 +2267,7 @@
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/DeliveryHeader.yaml</t>
+          <t>mapping\impix\erp\DeliveryHeader.yaml</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr"/>
@@ -2307,7 +2319,7 @@
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/DeliveryLine.yaml</t>
+          <t>mapping\impix\erp\DeliveryLine.yaml</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr"/>
@@ -2359,7 +2371,7 @@
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/PurchaseOrderHeader.yaml</t>
+          <t>mapping\impix\erp\PurchaseOrderHeader.yaml</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr"/>
@@ -2415,7 +2427,7 @@
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/PurchaseOrderLine.yaml</t>
+          <t>mapping\impix\erp\PurchaseOrderLine.yaml</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
@@ -2467,7 +2479,7 @@
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/GoodsReceipt.yaml</t>
+          <t>mapping\impix\erp\GoodsReceipt.yaml</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
@@ -2519,7 +2531,7 @@
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/GoodsIssue.yaml</t>
+          <t>mapping\impix\erp\GoodsIssue.yaml</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
@@ -2579,7 +2591,7 @@
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/ProductionPlanning.yaml</t>
+          <t>mapping\impix\erp\ProductionPlanning.yaml</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr"/>
@@ -2631,7 +2643,7 @@
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/ProductionOrder.yaml</t>
+          <t>mapping\impix\erp\ProductionOrder.yaml</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
@@ -2683,7 +2695,7 @@
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/ProductIncoming.yaml</t>
+          <t>mapping\impix\erp\ProductIncoming.yaml</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr"/>
@@ -2739,7 +2751,7 @@
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/AvailableInventory.yaml</t>
+          <t>mapping\impix\erp\AvailableInventory.yaml</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr"/>
@@ -2795,7 +2807,7 @@
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/Inventory.yaml</t>
+          <t>mapping\impix\erp\Inventory.yaml</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr"/>
@@ -2847,7 +2859,7 @@
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/InventorySnapshot.yaml</t>
+          <t>mapping\impix\erp\InventorySnapshot.yaml</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr"/>
@@ -2899,7 +2911,7 @@
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/LotInventory.yaml</t>
+          <t>mapping\impix\erp\LotInventory.yaml</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr"/>
@@ -2951,7 +2963,7 @@
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/erp/InventoryCount.yaml</t>
+          <t>mapping\impix\erp\InventoryCount.yaml</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
@@ -3003,7 +3015,7 @@
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/mes/Lot.yaml</t>
+          <t>mapping\impix\mes\Lot.yaml</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr"/>
@@ -3055,7 +3067,7 @@
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/mes/OperationStart.yaml</t>
+          <t>mapping\impix\mes\OperationStart.yaml</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
@@ -3111,7 +3123,7 @@
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/mes/OperationEnd.yaml</t>
+          <t>mapping\impix\mes\OperationEnd.yaml</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr"/>
@@ -3167,7 +3179,7 @@
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/mes/ProductionPerformance.yaml</t>
+          <t>mapping\impix\mes\ProductionPerformance.yaml</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr"/>
@@ -3223,7 +3235,7 @@
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/mes/ProductionPerformanceEquipment.yaml</t>
+          <t>mapping\impix\mes\ProductionPerformanceEquipment.yaml</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr"/>
@@ -3279,7 +3291,7 @@
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/mes/ProductionPerformanceQuality.yaml</t>
+          <t>mapping\impix\mes\ProductionPerformanceQuality.yaml</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr"/>
@@ -3339,7 +3351,7 @@
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/mes/ProductionPerformanceItem.yaml</t>
+          <t>mapping\impix\mes\ProductionPerformanceItem.yaml</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr"/>
@@ -3395,7 +3407,7 @@
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/mes/EquipmentState.yaml</t>
+          <t>mapping\impix\mes\EquipmentState.yaml</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr"/>
@@ -3451,7 +3463,7 @@
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/mes/Alarm.yaml</t>
+          <t>mapping\impix\mes\Alarm.yaml</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr"/>
@@ -3507,7 +3519,7 @@
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/mes/TraceParameter.yaml</t>
+          <t>mapping\impix\mes\TraceParameter.yaml</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr"/>
@@ -3559,7 +3571,7 @@
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/qms/CustomerComplaint.yaml</t>
+          <t>mapping\impix\qms\CustomerComplaint.yaml</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr"/>
@@ -3615,7 +3627,7 @@
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/qms/Return.yaml</t>
+          <t>mapping\impix\qms\Return.yaml</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr"/>
@@ -3671,7 +3683,7 @@
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/qms/SupplierInspectionResult.yaml</t>
+          <t>mapping\impix\qms\SupplierInspectionResult.yaml</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr"/>
@@ -3723,7 +3735,7 @@
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/qms/CorrectiveActionRequest.yaml</t>
+          <t>mapping\impix\qms\CorrectiveActionRequest.yaml</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr"/>
@@ -3779,7 +3791,7 @@
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/qms/CorrectiveActionResult.yaml</t>
+          <t>mapping\impix\qms\CorrectiveActionResult.yaml</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr"/>
@@ -3831,7 +3843,7 @@
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/qms/GoodsIssue_scrap.yaml</t>
+          <t>mapping\impix\qms\GoodsIssue_scrap.yaml</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr"/>
@@ -3883,7 +3895,7 @@
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>mapping/impix/qms/QualityCost.yaml</t>
+          <t>mapping\impix\qms\QualityCost.yaml</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr"/>
@@ -16896,12 +16908,12 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>⑥⑦ 검토자</t>
+          <t>② 정규화</t>
         </is>
       </c>
       <c r="I222" s="3" t="inlineStr">
         <is>
-          <t>결정론 미해소 → 검토자 판단</t>
+          <t>so_dt → SalesDate</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr"/>
@@ -16957,12 +16969,12 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>④ 국문명</t>
+          <t>② 정규화</t>
         </is>
       </c>
       <c r="I223" s="3" t="inlineStr">
         <is>
-          <t>주석 '수주상태(SO_STAT)' = 수주상태</t>
+          <t>so_stat → SalesStatus</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr">

--- a/mapping/impix/S2_매핑정의서_IMPIX.xlsx
+++ b/mapping/impix/S2_매핑정의서_IMPIX.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 18:20 · tools/automap · 계획 mapping/impix/s2_plan.yaml</t>
+          <t>2026-10-23 18:26 · tools/automap · 계획 mapping/impix/s2_plan.yaml</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>reviewed(데이터 엔지니어 검토) — 도메인·현업 승인 대기</t>
+          <t>approved — 업무 승인 2026-10-23 (승인 시트·S2_승인기록.md)</t>
         </is>
       </c>
     </row>
@@ -771,9 +771,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -804,9 +804,21 @@
           <t>데이터 엔지니어(reviewed)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Claude(자동 매핑·검토)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>완료 기준 3종 충족, 로트 A안 반영</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -814,9 +826,21 @@
           <t>도메인(PI) 컨설턴트(approved)</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>장홍관</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>S2 승인 — PM·도메인·현업 겸임(가상 실습)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -824,9 +848,21 @@
           <t>고객사 현업 검수자(approved)</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>장홍관(겸임)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>근사 대응 4건·확장·구조 판단 확인</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D4"/>
@@ -4230,7 +4266,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr"/>
@@ -4291,7 +4327,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr"/>
@@ -4352,7 +4388,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr"/>
@@ -4409,7 +4445,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr"/>
@@ -4466,7 +4502,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr"/>
@@ -4523,7 +4559,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr"/>
@@ -4580,7 +4616,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr"/>
@@ -4641,7 +4677,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr"/>
@@ -4698,7 +4734,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr"/>
@@ -4755,7 +4791,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr"/>
@@ -4812,7 +4848,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr"/>
@@ -4869,7 +4905,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr"/>
@@ -4930,7 +4966,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr"/>
@@ -4991,7 +5027,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr"/>
@@ -5052,7 +5088,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr"/>
@@ -5109,7 +5145,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr"/>
@@ -5166,7 +5202,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr"/>
@@ -5223,7 +5259,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr"/>
@@ -5280,7 +5316,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr"/>
@@ -5341,7 +5377,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr"/>
@@ -5402,7 +5438,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr"/>
@@ -5463,7 +5499,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr"/>
@@ -5524,7 +5560,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr"/>
@@ -5581,7 +5617,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr"/>
@@ -5638,7 +5674,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr"/>
@@ -5695,7 +5731,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr"/>
@@ -5748,7 +5784,7 @@
       <c r="M28" s="3" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr"/>
@@ -5801,7 +5837,7 @@
       <c r="M29" s="3" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr"/>
@@ -5862,7 +5898,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr"/>
@@ -5923,7 +5959,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr"/>
@@ -5980,7 +6016,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr"/>
@@ -6037,7 +6073,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr"/>
@@ -6090,7 +6126,7 @@
       <c r="M34" s="3" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr"/>
@@ -6143,7 +6179,7 @@
       <c r="M35" s="3" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr"/>
@@ -6204,7 +6240,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr"/>
@@ -6265,7 +6301,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr"/>
@@ -6322,7 +6358,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr"/>
@@ -6379,7 +6415,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr"/>
@@ -6440,7 +6476,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr"/>
@@ -6497,7 +6533,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr"/>
@@ -6554,7 +6590,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr"/>
@@ -6607,7 +6643,7 @@
       <c r="M43" s="3" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr"/>
@@ -6660,7 +6696,7 @@
       <c r="M44" s="3" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr"/>
@@ -6721,7 +6757,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr"/>
@@ -6782,7 +6818,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr"/>
@@ -6843,7 +6879,7 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr"/>
@@ -6908,7 +6944,7 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr"/>
@@ -6965,7 +7001,7 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr"/>
@@ -7026,7 +7062,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr"/>
@@ -7087,7 +7123,7 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr"/>
@@ -7144,7 +7180,7 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr"/>
@@ -7201,7 +7237,7 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr"/>
@@ -7262,7 +7298,7 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr"/>
@@ -7323,7 +7359,7 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
@@ -7384,7 +7420,7 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr"/>
@@ -7445,7 +7481,7 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr"/>
@@ -7502,7 +7538,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr"/>
@@ -7563,7 +7599,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr"/>
@@ -7624,7 +7660,7 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr"/>
@@ -7685,7 +7721,7 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr"/>
@@ -7742,7 +7778,7 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr"/>
@@ -7799,7 +7835,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr"/>
@@ -7860,7 +7896,7 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr"/>
@@ -7921,7 +7957,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr"/>
@@ -7982,7 +8018,7 @@
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr"/>
@@ -8035,7 +8071,7 @@
       <c r="M67" s="3" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr"/>
@@ -8088,7 +8124,7 @@
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr"/>
@@ -8149,7 +8185,7 @@
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O69" s="3" t="inlineStr"/>
@@ -8214,7 +8250,7 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
@@ -8279,7 +8315,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O71" s="3" t="inlineStr"/>
@@ -8340,7 +8376,7 @@
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr"/>
@@ -8401,7 +8437,7 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr"/>
@@ -8458,7 +8494,7 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr"/>
@@ -8519,7 +8555,7 @@
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O75" s="3" t="inlineStr"/>
@@ -8576,7 +8612,7 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr"/>
@@ -8629,7 +8665,7 @@
       <c r="M77" s="3" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O77" s="3" t="inlineStr"/>
@@ -8682,7 +8718,7 @@
       <c r="M78" s="3" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr"/>
@@ -8743,7 +8779,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O79" s="3" t="inlineStr"/>
@@ -8808,7 +8844,7 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr"/>
@@ -8869,7 +8905,7 @@
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O81" s="3" t="inlineStr"/>
@@ -8930,7 +8966,7 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr"/>
@@ -8991,7 +9027,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr"/>
@@ -9052,7 +9088,7 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr"/>
@@ -9109,7 +9145,7 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O85" s="3" t="inlineStr"/>
@@ -9166,7 +9202,7 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O86" s="3" t="inlineStr"/>
@@ -9227,7 +9263,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O87" s="3" t="inlineStr"/>
@@ -9288,7 +9324,7 @@
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr"/>
@@ -9349,7 +9385,7 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O89" s="3" t="inlineStr">
@@ -9406,7 +9442,7 @@
       <c r="M90" s="3" t="inlineStr"/>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O90" s="3" t="inlineStr"/>
@@ -9459,7 +9495,7 @@
       <c r="M91" s="3" t="inlineStr"/>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O91" s="3" t="inlineStr"/>
@@ -9520,7 +9556,7 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O92" s="3" t="inlineStr"/>
@@ -9581,7 +9617,7 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O93" s="3" t="inlineStr"/>
@@ -9638,7 +9674,7 @@
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr"/>
@@ -9699,7 +9735,7 @@
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O95" s="3" t="inlineStr"/>
@@ -9760,7 +9796,7 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr"/>
@@ -9813,7 +9849,7 @@
       <c r="M97" s="3" t="inlineStr"/>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O97" s="3" t="inlineStr"/>
@@ -9866,7 +9902,7 @@
       <c r="M98" s="3" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O98" s="3" t="inlineStr"/>
@@ -9927,7 +9963,7 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O99" s="3" t="inlineStr"/>
@@ -9988,7 +10024,7 @@
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O100" s="3" t="inlineStr"/>
@@ -10049,7 +10085,7 @@
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O101" s="3" t="inlineStr"/>
@@ -10106,7 +10142,7 @@
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O102" s="3" t="inlineStr">
@@ -10171,7 +10207,7 @@
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O103" s="3" t="inlineStr"/>
@@ -10232,7 +10268,7 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O104" s="3" t="inlineStr"/>
@@ -10293,7 +10329,7 @@
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O105" s="3" t="inlineStr">
@@ -10358,7 +10394,7 @@
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O106" s="3" t="inlineStr"/>
@@ -10411,7 +10447,7 @@
       <c r="M107" s="3" t="inlineStr"/>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O107" s="3" t="inlineStr"/>
@@ -10464,7 +10500,7 @@
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O108" s="3" t="inlineStr"/>
@@ -10525,7 +10561,7 @@
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O109" s="3" t="inlineStr"/>
@@ -10586,7 +10622,7 @@
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O110" s="3" t="inlineStr"/>
@@ -10643,7 +10679,7 @@
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O111" s="3" t="inlineStr"/>
@@ -10704,7 +10740,7 @@
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O112" s="3" t="inlineStr"/>
@@ -10765,7 +10801,7 @@
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O113" s="3" t="inlineStr"/>
@@ -10818,7 +10854,7 @@
       <c r="M114" s="3" t="inlineStr"/>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O114" s="3" t="inlineStr"/>
@@ -10871,7 +10907,7 @@
       <c r="M115" s="3" t="inlineStr"/>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O115" s="3" t="inlineStr"/>
@@ -10932,7 +10968,7 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O116" s="3" t="inlineStr"/>
@@ -10993,7 +11029,7 @@
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O117" s="3" t="inlineStr"/>
@@ -11050,7 +11086,7 @@
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O118" s="3" t="inlineStr"/>
@@ -11111,7 +11147,7 @@
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O119" s="3" t="inlineStr"/>
@@ -11168,7 +11204,7 @@
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O120" s="3" t="inlineStr">
@@ -11233,7 +11269,7 @@
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O121" s="3" t="inlineStr">
@@ -11294,7 +11330,7 @@
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O122" s="3" t="inlineStr"/>
@@ -11355,7 +11391,7 @@
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O123" s="3" t="inlineStr"/>
@@ -11408,7 +11444,7 @@
       <c r="M124" s="3" t="inlineStr"/>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O124" s="3" t="inlineStr"/>
@@ -11461,7 +11497,7 @@
       <c r="M125" s="3" t="inlineStr"/>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O125" s="3" t="inlineStr"/>
@@ -11522,7 +11558,7 @@
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O126" s="3" t="inlineStr"/>
@@ -11583,7 +11619,7 @@
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O127" s="3" t="inlineStr"/>
@@ -11640,7 +11676,7 @@
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O128" s="3" t="inlineStr"/>
@@ -11701,7 +11737,7 @@
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O129" s="3" t="inlineStr"/>
@@ -11762,7 +11798,7 @@
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O130" s="3" t="inlineStr"/>
@@ -11815,7 +11851,7 @@
       <c r="M131" s="3" t="inlineStr"/>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O131" s="3" t="inlineStr"/>
@@ -11868,7 +11904,7 @@
       <c r="M132" s="3" t="inlineStr"/>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O132" s="3" t="inlineStr"/>
@@ -11929,7 +11965,7 @@
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O133" s="3" t="inlineStr"/>
@@ -11990,7 +12026,7 @@
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O134" s="3" t="inlineStr"/>
@@ -12047,7 +12083,7 @@
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O135" s="3" t="inlineStr"/>
@@ -12108,7 +12144,7 @@
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O136" s="3" t="inlineStr"/>
@@ -12169,7 +12205,7 @@
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O137" s="3" t="inlineStr"/>
@@ -12226,7 +12262,7 @@
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O138" s="3" t="inlineStr"/>
@@ -12283,7 +12319,7 @@
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O139" s="3" t="inlineStr"/>
@@ -12344,7 +12380,7 @@
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O140" s="3" t="inlineStr"/>
@@ -12401,7 +12437,7 @@
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O141" s="3" t="inlineStr">
@@ -12462,7 +12498,7 @@
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O142" s="3" t="inlineStr"/>
@@ -12519,7 +12555,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O143" s="3" t="inlineStr"/>
@@ -12576,7 +12612,7 @@
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O144" s="3" t="inlineStr"/>
@@ -12637,7 +12673,7 @@
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O145" s="3" t="inlineStr">
@@ -12694,7 +12730,7 @@
       <c r="M146" s="3" t="inlineStr"/>
       <c r="N146" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O146" s="3" t="inlineStr"/>
@@ -12747,7 +12783,7 @@
       <c r="M147" s="3" t="inlineStr"/>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O147" s="3" t="inlineStr"/>
@@ -12808,7 +12844,7 @@
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O148" s="3" t="inlineStr"/>
@@ -12869,7 +12905,7 @@
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O149" s="3" t="inlineStr"/>
@@ -12930,7 +12966,7 @@
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O150" s="3" t="inlineStr"/>
@@ -12987,7 +13023,7 @@
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O151" s="3" t="inlineStr"/>
@@ -13040,7 +13076,7 @@
       <c r="M152" s="3" t="inlineStr"/>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O152" s="3" t="inlineStr"/>
@@ -13093,7 +13129,7 @@
       <c r="M153" s="3" t="inlineStr"/>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O153" s="3" t="inlineStr"/>
@@ -13146,7 +13182,7 @@
       <c r="M154" s="3" t="inlineStr"/>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O154" s="3" t="inlineStr"/>
@@ -13207,7 +13243,7 @@
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O155" s="3" t="inlineStr"/>
@@ -13264,7 +13300,7 @@
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O156" s="3" t="inlineStr"/>
@@ -13321,7 +13357,7 @@
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O157" s="3" t="inlineStr"/>
@@ -13382,7 +13418,7 @@
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O158" s="3" t="inlineStr"/>
@@ -13443,7 +13479,7 @@
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O159" s="3" t="inlineStr"/>
@@ -13500,7 +13536,7 @@
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O160" s="3" t="inlineStr"/>
@@ -13557,7 +13593,7 @@
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O161" s="3" t="inlineStr"/>
@@ -13618,7 +13654,7 @@
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O162" s="3" t="inlineStr"/>
@@ -13671,7 +13707,7 @@
       <c r="M163" s="3" t="inlineStr"/>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O163" s="3" t="inlineStr"/>
@@ -13724,7 +13760,7 @@
       <c r="M164" s="3" t="inlineStr"/>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O164" s="3" t="inlineStr"/>
@@ -13777,7 +13813,7 @@
       <c r="M165" s="3" t="inlineStr"/>
       <c r="N165" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O165" s="3" t="inlineStr"/>
@@ -13838,7 +13874,7 @@
       </c>
       <c r="N166" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O166" s="3" t="inlineStr"/>
@@ -13895,7 +13931,7 @@
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O167" s="3" t="inlineStr"/>
@@ -13952,7 +13988,7 @@
       </c>
       <c r="N168" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O168" s="3" t="inlineStr"/>
@@ -14013,7 +14049,7 @@
       </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O169" s="3" t="inlineStr"/>
@@ -14070,7 +14106,7 @@
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O170" s="3" t="inlineStr"/>
@@ -14127,7 +14163,7 @@
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O171" s="3" t="inlineStr"/>
@@ -14180,7 +14216,7 @@
       <c r="M172" s="3" t="inlineStr"/>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O172" s="3" t="inlineStr"/>
@@ -14233,7 +14269,7 @@
       <c r="M173" s="3" t="inlineStr"/>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O173" s="3" t="inlineStr"/>
@@ -14286,7 +14322,7 @@
       <c r="M174" s="3" t="inlineStr"/>
       <c r="N174" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O174" s="3" t="inlineStr"/>
@@ -14351,7 +14387,7 @@
       </c>
       <c r="N175" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O175" s="3" t="inlineStr"/>
@@ -14416,7 +14452,7 @@
       </c>
       <c r="N176" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O176" s="3" t="inlineStr"/>
@@ -14473,7 +14509,7 @@
       </c>
       <c r="N177" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O177" s="3" t="inlineStr"/>
@@ -14526,7 +14562,7 @@
       <c r="M178" s="3" t="inlineStr"/>
       <c r="N178" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O178" s="3" t="inlineStr"/>
@@ -14579,7 +14615,7 @@
       <c r="M179" s="3" t="inlineStr"/>
       <c r="N179" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O179" s="3" t="inlineStr"/>
@@ -14640,7 +14676,7 @@
       </c>
       <c r="N180" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O180" s="3" t="inlineStr"/>
@@ -14701,7 +14737,7 @@
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O181" s="3" t="inlineStr"/>
@@ -14766,7 +14802,7 @@
       </c>
       <c r="N182" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O182" s="3" t="inlineStr"/>
@@ -14831,7 +14867,7 @@
       </c>
       <c r="N183" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O183" s="3" t="inlineStr"/>
@@ -14892,7 +14928,7 @@
       </c>
       <c r="N184" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O184" s="3" t="inlineStr"/>
@@ -14953,7 +14989,7 @@
       </c>
       <c r="N185" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O185" s="3" t="inlineStr"/>
@@ -15010,7 +15046,7 @@
       </c>
       <c r="N186" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O186" s="3" t="inlineStr"/>
@@ -15067,7 +15103,7 @@
       </c>
       <c r="N187" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O187" s="3" t="inlineStr"/>
@@ -15124,7 +15160,7 @@
       </c>
       <c r="N188" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O188" s="3" t="inlineStr"/>
@@ -15185,7 +15221,7 @@
       </c>
       <c r="N189" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O189" s="3" t="inlineStr"/>
@@ -15238,7 +15274,7 @@
       <c r="M190" s="3" t="inlineStr"/>
       <c r="N190" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O190" s="3" t="inlineStr"/>
@@ -15291,7 +15327,7 @@
       <c r="M191" s="3" t="inlineStr"/>
       <c r="N191" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O191" s="3" t="inlineStr"/>
@@ -15352,7 +15388,7 @@
       </c>
       <c r="N192" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O192" s="3" t="inlineStr"/>
@@ -15413,7 +15449,7 @@
       </c>
       <c r="N193" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O193" s="3" t="inlineStr"/>
@@ -15470,7 +15506,7 @@
       </c>
       <c r="N194" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O194" s="3" t="inlineStr"/>
@@ -15531,7 +15567,7 @@
       </c>
       <c r="N195" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O195" s="3" t="inlineStr"/>
@@ -15592,7 +15628,7 @@
       </c>
       <c r="N196" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O196" s="3" t="inlineStr"/>
@@ -15653,7 +15689,7 @@
       </c>
       <c r="N197" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O197" s="3" t="inlineStr"/>
@@ -15710,7 +15746,7 @@
       </c>
       <c r="N198" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O198" s="3" t="inlineStr"/>
@@ -15767,7 +15803,7 @@
       </c>
       <c r="N199" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O199" s="3" t="inlineStr"/>
@@ -15824,7 +15860,7 @@
       </c>
       <c r="N200" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O200" s="3" t="inlineStr"/>
@@ -15885,7 +15921,7 @@
       </c>
       <c r="N201" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O201" s="3" t="inlineStr"/>
@@ -15946,7 +15982,7 @@
       </c>
       <c r="N202" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O202" s="3" t="inlineStr"/>
@@ -16003,7 +16039,7 @@
       </c>
       <c r="N203" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O203" s="3" t="inlineStr"/>
@@ -16060,7 +16096,7 @@
       </c>
       <c r="N204" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O204" s="3" t="inlineStr"/>
@@ -16113,7 +16149,7 @@
       <c r="M205" s="3" t="inlineStr"/>
       <c r="N205" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O205" s="3" t="inlineStr"/>
@@ -16166,7 +16202,7 @@
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O206" s="3" t="inlineStr"/>
@@ -16219,7 +16255,7 @@
       <c r="M207" s="3" t="inlineStr"/>
       <c r="N207" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O207" s="3" t="inlineStr"/>
@@ -16280,7 +16316,7 @@
       </c>
       <c r="N208" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O208" s="3" t="inlineStr"/>
@@ -16341,7 +16377,7 @@
       <c r="M209" s="3" t="inlineStr"/>
       <c r="N209" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O209" s="3" t="inlineStr"/>
@@ -16402,7 +16438,7 @@
       </c>
       <c r="N210" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O210" s="3" t="inlineStr"/>
@@ -16459,7 +16495,7 @@
       </c>
       <c r="N211" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O211" s="3" t="inlineStr"/>
@@ -16520,7 +16556,7 @@
       </c>
       <c r="N212" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O212" s="3" t="inlineStr"/>
@@ -16581,7 +16617,7 @@
       </c>
       <c r="N213" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O213" s="3" t="inlineStr"/>
@@ -16646,7 +16682,7 @@
       </c>
       <c r="N214" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O214" s="3" t="inlineStr"/>
@@ -16703,7 +16739,7 @@
       </c>
       <c r="N215" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O215" s="3" t="inlineStr"/>
@@ -16760,7 +16796,7 @@
       </c>
       <c r="N216" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O216" s="3" t="inlineStr"/>
@@ -16813,7 +16849,7 @@
       <c r="M217" s="3" t="inlineStr"/>
       <c r="N217" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O217" s="3" t="inlineStr"/>
@@ -16866,7 +16902,7 @@
       <c r="M218" s="3" t="inlineStr"/>
       <c r="N218" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O218" s="3" t="inlineStr"/>
@@ -16919,7 +16955,7 @@
       <c r="M219" s="3" t="inlineStr"/>
       <c r="N219" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O219" s="3" t="inlineStr"/>
@@ -16976,7 +17012,7 @@
       </c>
       <c r="N220" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O220" s="3" t="inlineStr"/>
@@ -17037,7 +17073,7 @@
       </c>
       <c r="N221" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O221" s="3" t="inlineStr"/>
@@ -17098,7 +17134,7 @@
       </c>
       <c r="N222" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O222" s="3" t="inlineStr"/>
@@ -17155,7 +17191,7 @@
       </c>
       <c r="N223" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O223" s="3" t="inlineStr"/>
@@ -17216,7 +17252,7 @@
       </c>
       <c r="N224" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O224" s="3" t="inlineStr"/>
@@ -17277,7 +17313,7 @@
       </c>
       <c r="N225" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O225" s="3" t="inlineStr"/>
@@ -17330,7 +17366,7 @@
       <c r="M226" s="3" t="inlineStr"/>
       <c r="N226" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O226" s="3" t="inlineStr"/>
@@ -17383,7 +17419,7 @@
       <c r="M227" s="3" t="inlineStr"/>
       <c r="N227" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O227" s="3" t="inlineStr"/>
@@ -17436,7 +17472,7 @@
       <c r="M228" s="3" t="inlineStr"/>
       <c r="N228" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O228" s="3" t="inlineStr"/>
@@ -17497,7 +17533,7 @@
       </c>
       <c r="N229" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O229" s="3" t="inlineStr"/>
@@ -17558,7 +17594,7 @@
       </c>
       <c r="N230" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O230" s="3" t="inlineStr"/>
@@ -17619,7 +17655,7 @@
       </c>
       <c r="N231" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O231" s="3" t="inlineStr"/>
@@ -17676,7 +17712,7 @@
       </c>
       <c r="N232" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O232" s="3" t="inlineStr"/>
@@ -17737,7 +17773,7 @@
       </c>
       <c r="N233" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O233" s="3" t="inlineStr"/>
@@ -17798,7 +17834,7 @@
       </c>
       <c r="N234" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O234" s="3" t="inlineStr"/>
@@ -17855,7 +17891,7 @@
       </c>
       <c r="N235" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O235" s="3" t="inlineStr"/>
@@ -17904,7 +17940,7 @@
       <c r="M236" s="3" t="inlineStr"/>
       <c r="N236" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O236" s="3" t="inlineStr">
@@ -17965,7 +18001,7 @@
       <c r="M237" s="3" t="inlineStr"/>
       <c r="N237" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O237" s="3" t="inlineStr"/>
@@ -18018,7 +18054,7 @@
       <c r="M238" s="3" t="inlineStr"/>
       <c r="N238" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O238" s="3" t="inlineStr"/>
@@ -18071,7 +18107,7 @@
       <c r="M239" s="3" t="inlineStr"/>
       <c r="N239" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O239" s="3" t="inlineStr"/>
@@ -18132,7 +18168,7 @@
       </c>
       <c r="N240" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O240" s="3" t="inlineStr"/>
@@ -18193,7 +18229,7 @@
       </c>
       <c r="N241" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O241" s="3" t="inlineStr"/>
@@ -18246,7 +18282,7 @@
       <c r="M242" s="3" t="inlineStr"/>
       <c r="N242" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O242" s="3" t="inlineStr">
@@ -18307,7 +18343,7 @@
       </c>
       <c r="N243" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O243" s="3" t="inlineStr"/>
@@ -18364,7 +18400,7 @@
       </c>
       <c r="N244" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O244" s="3" t="inlineStr"/>
@@ -18425,7 +18461,7 @@
       </c>
       <c r="N245" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O245" s="3" t="inlineStr"/>
@@ -18486,7 +18522,7 @@
       </c>
       <c r="N246" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O246" s="3" t="inlineStr"/>
@@ -18543,7 +18579,7 @@
       </c>
       <c r="N247" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O247" s="3" t="inlineStr"/>
@@ -18604,7 +18640,7 @@
       </c>
       <c r="N248" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O248" s="3" t="inlineStr"/>
@@ -18661,7 +18697,7 @@
       </c>
       <c r="N249" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O249" s="3" t="inlineStr"/>
@@ -18718,7 +18754,7 @@
       </c>
       <c r="N250" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O250" s="3" t="inlineStr"/>
@@ -18775,7 +18811,7 @@
       </c>
       <c r="N251" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O251" s="3" t="inlineStr"/>
@@ -18828,7 +18864,7 @@
       <c r="M252" s="3" t="inlineStr"/>
       <c r="N252" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O252" s="3" t="inlineStr"/>
@@ -18881,7 +18917,7 @@
       <c r="M253" s="3" t="inlineStr"/>
       <c r="N253" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O253" s="3" t="inlineStr"/>
@@ -18942,7 +18978,7 @@
       </c>
       <c r="N254" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O254" s="3" t="inlineStr"/>
@@ -19003,7 +19039,7 @@
       </c>
       <c r="N255" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O255" s="3" t="inlineStr"/>
@@ -19064,7 +19100,7 @@
       </c>
       <c r="N256" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O256" s="3" t="inlineStr"/>
@@ -19121,7 +19157,7 @@
       </c>
       <c r="N257" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O257" s="3" t="inlineStr"/>
@@ -19174,7 +19210,7 @@
       <c r="M258" s="3" t="inlineStr"/>
       <c r="N258" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O258" s="3" t="inlineStr"/>
@@ -19227,7 +19263,7 @@
       <c r="M259" s="3" t="inlineStr"/>
       <c r="N259" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O259" s="3" t="inlineStr"/>
@@ -19288,7 +19324,7 @@
       </c>
       <c r="N260" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O260" s="3" t="inlineStr"/>
@@ -19349,7 +19385,7 @@
       </c>
       <c r="N261" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O261" s="3" t="inlineStr"/>
@@ -19402,7 +19438,7 @@
       <c r="M262" s="3" t="inlineStr"/>
       <c r="N262" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O262" s="3" t="inlineStr"/>
@@ -19459,7 +19495,7 @@
       </c>
       <c r="N263" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O263" s="3" t="inlineStr"/>
@@ -19508,7 +19544,7 @@
       <c r="M264" s="3" t="inlineStr"/>
       <c r="N264" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O264" s="3" t="inlineStr"/>
@@ -19565,7 +19601,7 @@
       </c>
       <c r="N265" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O265" s="3" t="inlineStr"/>
@@ -19622,7 +19658,7 @@
       </c>
       <c r="N266" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O266" s="3" t="inlineStr"/>
@@ -19683,7 +19719,7 @@
       </c>
       <c r="N267" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O267" s="3" t="inlineStr"/>
@@ -19740,7 +19776,7 @@
       </c>
       <c r="N268" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O268" s="3" t="inlineStr"/>
@@ -19797,7 +19833,7 @@
       </c>
       <c r="N269" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O269" s="3" t="inlineStr"/>
@@ -19850,7 +19886,7 @@
       <c r="M270" s="3" t="inlineStr"/>
       <c r="N270" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O270" s="3" t="inlineStr"/>
@@ -19903,7 +19939,7 @@
       <c r="M271" s="3" t="inlineStr"/>
       <c r="N271" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O271" s="3" t="inlineStr"/>
@@ -19956,7 +19992,7 @@
       <c r="M272" s="3" t="inlineStr"/>
       <c r="N272" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O272" s="3" t="inlineStr"/>
@@ -20017,7 +20053,7 @@
       </c>
       <c r="N273" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O273" s="3" t="inlineStr"/>
@@ -20074,7 +20110,7 @@
       </c>
       <c r="N274" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O274" s="3" t="inlineStr"/>
@@ -20135,7 +20171,7 @@
       </c>
       <c r="N275" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O275" s="3" t="inlineStr"/>
@@ -20192,7 +20228,7 @@
       </c>
       <c r="N276" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O276" s="3" t="inlineStr"/>
@@ -20253,7 +20289,7 @@
       </c>
       <c r="N277" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O277" s="3" t="inlineStr">
@@ -20310,7 +20346,7 @@
       <c r="M278" s="3" t="inlineStr"/>
       <c r="N278" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O278" s="3" t="inlineStr"/>
@@ -20363,7 +20399,7 @@
       <c r="M279" s="3" t="inlineStr"/>
       <c r="N279" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O279" s="3" t="inlineStr"/>
@@ -20416,7 +20452,7 @@
       <c r="M280" s="3" t="inlineStr"/>
       <c r="N280" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O280" s="3" t="inlineStr"/>
@@ -20477,7 +20513,7 @@
       </c>
       <c r="N281" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O281" s="3" t="inlineStr"/>
@@ -20538,7 +20574,7 @@
       </c>
       <c r="N282" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O282" s="3" t="inlineStr"/>
@@ -20599,7 +20635,7 @@
       </c>
       <c r="N283" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O283" s="3" t="inlineStr"/>
@@ -20660,7 +20696,7 @@
       </c>
       <c r="N284" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O284" s="3" t="inlineStr">
@@ -20721,7 +20757,7 @@
       </c>
       <c r="N285" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O285" s="3" t="inlineStr"/>
@@ -20778,7 +20814,7 @@
       </c>
       <c r="N286" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O286" s="3" t="inlineStr"/>
@@ -20835,7 +20871,7 @@
       </c>
       <c r="N287" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O287" s="3" t="inlineStr"/>
@@ -20896,7 +20932,7 @@
       </c>
       <c r="N288" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O288" s="3" t="inlineStr"/>
@@ -20949,7 +20985,7 @@
       <c r="M289" s="3" t="inlineStr"/>
       <c r="N289" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O289" s="3" t="inlineStr"/>
@@ -21002,7 +21038,7 @@
       <c r="M290" s="3" t="inlineStr"/>
       <c r="N290" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O290" s="3" t="inlineStr"/>
@@ -21063,7 +21099,7 @@
       </c>
       <c r="N291" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O291" s="3" t="inlineStr"/>
@@ -21124,7 +21160,7 @@
       </c>
       <c r="N292" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O292" s="3" t="inlineStr"/>
@@ -21181,7 +21217,7 @@
       </c>
       <c r="N293" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O293" s="3" t="inlineStr"/>
@@ -21234,7 +21270,7 @@
       <c r="M294" s="3" t="inlineStr"/>
       <c r="N294" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O294" s="3" t="inlineStr"/>
@@ -21295,7 +21331,7 @@
       </c>
       <c r="N295" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O295" s="3" t="inlineStr"/>
@@ -21356,7 +21392,7 @@
       </c>
       <c r="N296" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O296" s="3" t="inlineStr"/>
@@ -21417,7 +21453,7 @@
       </c>
       <c r="N297" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O297" s="3" t="inlineStr"/>
@@ -21474,7 +21510,7 @@
       </c>
       <c r="N298" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O298" s="3" t="inlineStr"/>
@@ -21531,7 +21567,7 @@
       </c>
       <c r="N299" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O299" s="3" t="inlineStr"/>
@@ -21588,7 +21624,7 @@
       <c r="M300" s="3" t="inlineStr"/>
       <c r="N300" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O300" s="3" t="inlineStr">
@@ -21649,7 +21685,7 @@
       <c r="M301" s="3" t="inlineStr"/>
       <c r="N301" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O301" s="3" t="inlineStr"/>
@@ -21706,7 +21742,7 @@
       </c>
       <c r="N302" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O302" s="3" t="inlineStr"/>
@@ -21763,7 +21799,7 @@
       </c>
       <c r="N303" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O303" s="3" t="inlineStr"/>
@@ -21820,7 +21856,7 @@
       <c r="M304" s="3" t="inlineStr"/>
       <c r="N304" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O304" s="3" t="inlineStr">
@@ -21877,7 +21913,7 @@
       <c r="M305" s="3" t="inlineStr"/>
       <c r="N305" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O305" s="3" t="inlineStr"/>
@@ -21930,7 +21966,7 @@
       <c r="M306" s="3" t="inlineStr"/>
       <c r="N306" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O306" s="3" t="inlineStr"/>
@@ -21991,7 +22027,7 @@
       </c>
       <c r="N307" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O307" s="3" t="inlineStr"/>
@@ -22048,7 +22084,7 @@
       </c>
       <c r="N308" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O308" s="3" t="inlineStr"/>
@@ -22109,7 +22145,7 @@
       </c>
       <c r="N309" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O309" s="3" t="inlineStr"/>
@@ -22170,7 +22206,7 @@
       </c>
       <c r="N310" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O310" s="3" t="inlineStr"/>
@@ -22231,7 +22267,7 @@
       </c>
       <c r="N311" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O311" s="3" t="inlineStr"/>
@@ -22288,7 +22324,7 @@
       </c>
       <c r="N312" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O312" s="3" t="inlineStr"/>
@@ -22345,7 +22381,7 @@
       </c>
       <c r="N313" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O313" s="3" t="inlineStr"/>
@@ -22410,7 +22446,7 @@
       </c>
       <c r="N314" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O314" s="3" t="inlineStr"/>
@@ -22463,7 +22499,7 @@
       <c r="M315" s="3" t="inlineStr"/>
       <c r="N315" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O315" s="3" t="inlineStr"/>
@@ -22512,7 +22548,7 @@
       <c r="M316" s="3" t="inlineStr"/>
       <c r="N316" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O316" s="3" t="inlineStr">
@@ -22569,7 +22605,7 @@
       <c r="M317" s="3" t="inlineStr"/>
       <c r="N317" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O317" s="3" t="inlineStr"/>
@@ -22622,7 +22658,7 @@
       <c r="M318" s="3" t="inlineStr"/>
       <c r="N318" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O318" s="3" t="inlineStr"/>
@@ -22683,7 +22719,7 @@
       </c>
       <c r="N319" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O319" s="3" t="inlineStr"/>
@@ -22744,7 +22780,7 @@
       <c r="M320" s="3" t="inlineStr"/>
       <c r="N320" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O320" s="3" t="inlineStr"/>
@@ -22805,7 +22841,7 @@
       </c>
       <c r="N321" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O321" s="3" t="inlineStr"/>
@@ -22866,7 +22902,7 @@
       </c>
       <c r="N322" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O322" s="3" t="inlineStr"/>
@@ -22927,7 +22963,7 @@
       </c>
       <c r="N323" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O323" s="3" t="inlineStr"/>
@@ -22988,7 +23024,7 @@
       </c>
       <c r="N324" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O324" s="3" t="inlineStr"/>
@@ -23041,7 +23077,7 @@
       <c r="M325" s="3" t="inlineStr"/>
       <c r="N325" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O325" s="3" t="inlineStr"/>
@@ -23094,7 +23130,7 @@
       <c r="M326" s="3" t="inlineStr"/>
       <c r="N326" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O326" s="3" t="inlineStr"/>
@@ -23155,7 +23191,7 @@
       </c>
       <c r="N327" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O327" s="3" t="inlineStr"/>
@@ -23212,7 +23248,7 @@
       </c>
       <c r="N328" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O328" s="3" t="inlineStr"/>
@@ -23273,7 +23309,7 @@
       </c>
       <c r="N329" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O329" s="3" t="inlineStr"/>
@@ -23334,7 +23370,7 @@
       </c>
       <c r="N330" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O330" s="3" t="inlineStr"/>
@@ -23395,7 +23431,7 @@
       </c>
       <c r="N331" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O331" s="3" t="inlineStr"/>
@@ -23456,7 +23492,7 @@
       </c>
       <c r="N332" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O332" s="3" t="inlineStr"/>
@@ -23513,7 +23549,7 @@
       </c>
       <c r="N333" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O333" s="3" t="inlineStr"/>
@@ -23570,7 +23606,7 @@
       </c>
       <c r="N334" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O334" s="3" t="inlineStr"/>
@@ -23627,7 +23663,7 @@
       </c>
       <c r="N335" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O335" s="3" t="inlineStr"/>
@@ -23688,7 +23724,7 @@
       </c>
       <c r="N336" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O336" s="3" t="inlineStr"/>
@@ -23749,7 +23785,7 @@
       </c>
       <c r="N337" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O337" s="3" t="inlineStr"/>
@@ -23810,7 +23846,7 @@
       </c>
       <c r="N338" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O338" s="3" t="inlineStr"/>
@@ -23871,7 +23907,7 @@
       </c>
       <c r="N339" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O339" s="3" t="inlineStr"/>
@@ -23932,7 +23968,7 @@
       </c>
       <c r="N340" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O340" s="3" t="inlineStr"/>
@@ -23989,7 +24025,7 @@
       </c>
       <c r="N341" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O341" s="3" t="inlineStr"/>
@@ -24046,7 +24082,7 @@
       </c>
       <c r="N342" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O342" s="3" t="inlineStr"/>
@@ -24107,7 +24143,7 @@
       </c>
       <c r="N343" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O343" s="3" t="inlineStr"/>
@@ -24160,7 +24196,7 @@
       <c r="M344" s="3" t="inlineStr"/>
       <c r="N344" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O344" s="3" t="inlineStr"/>
@@ -24213,7 +24249,7 @@
       <c r="M345" s="3" t="inlineStr"/>
       <c r="N345" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O345" s="3" t="inlineStr"/>
@@ -24274,7 +24310,7 @@
       </c>
       <c r="N346" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O346" s="3" t="inlineStr"/>
@@ -24335,7 +24371,7 @@
       </c>
       <c r="N347" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O347" s="3" t="inlineStr"/>
@@ -24388,7 +24424,7 @@
       <c r="M348" s="3" t="inlineStr"/>
       <c r="N348" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O348" s="3" t="inlineStr"/>
@@ -24449,7 +24485,7 @@
       </c>
       <c r="N349" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O349" s="3" t="inlineStr"/>
@@ -24510,7 +24546,7 @@
       </c>
       <c r="N350" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O350" s="3" t="inlineStr"/>
@@ -24567,7 +24603,7 @@
       </c>
       <c r="N351" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O351" s="3" t="inlineStr"/>
@@ -24616,7 +24652,7 @@
       <c r="M352" s="3" t="inlineStr"/>
       <c r="N352" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O352" s="3" t="inlineStr">
@@ -24677,7 +24713,7 @@
       </c>
       <c r="N353" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O353" s="3" t="inlineStr"/>
@@ -24734,7 +24770,7 @@
       </c>
       <c r="N354" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O354" s="3" t="inlineStr"/>
@@ -24783,7 +24819,7 @@
       <c r="M355" s="3" t="inlineStr"/>
       <c r="N355" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O355" s="3" t="inlineStr"/>
@@ -24836,7 +24872,7 @@
       <c r="M356" s="3" t="inlineStr"/>
       <c r="N356" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O356" s="3" t="inlineStr"/>
@@ -24889,7 +24925,7 @@
       <c r="M357" s="3" t="inlineStr"/>
       <c r="N357" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O357" s="3" t="inlineStr"/>
@@ -24950,7 +24986,7 @@
       </c>
       <c r="N358" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O358" s="3" t="inlineStr"/>
@@ -25011,7 +25047,7 @@
       <c r="M359" s="3" t="inlineStr"/>
       <c r="N359" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O359" s="3" t="inlineStr"/>
@@ -25072,7 +25108,7 @@
       </c>
       <c r="N360" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O360" s="3" t="inlineStr">
@@ -25133,7 +25169,7 @@
       </c>
       <c r="N361" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O361" s="3" t="inlineStr"/>
@@ -25190,7 +25226,7 @@
       </c>
       <c r="N362" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O362" s="3" t="inlineStr"/>
@@ -25239,7 +25275,7 @@
       <c r="M363" s="3" t="inlineStr"/>
       <c r="N363" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O363" s="3" t="inlineStr"/>
@@ -25300,7 +25336,7 @@
       </c>
       <c r="N364" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O364" s="3" t="inlineStr">
@@ -25361,7 +25397,7 @@
       </c>
       <c r="N365" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O365" s="3" t="inlineStr"/>
@@ -25418,7 +25454,7 @@
       </c>
       <c r="N366" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O366" s="3" t="inlineStr"/>
@@ -25471,7 +25507,7 @@
       <c r="M367" s="3" t="inlineStr"/>
       <c r="N367" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O367" s="3" t="inlineStr"/>
@@ -25524,7 +25560,7 @@
       <c r="M368" s="3" t="inlineStr"/>
       <c r="N368" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O368" s="3" t="inlineStr"/>
@@ -25585,7 +25621,7 @@
       </c>
       <c r="N369" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O369" s="3" t="inlineStr"/>
@@ -25646,7 +25682,7 @@
       </c>
       <c r="N370" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O370" s="3" t="inlineStr"/>
@@ -25711,7 +25747,7 @@
       </c>
       <c r="N371" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O371" s="3" t="inlineStr"/>
@@ -25768,7 +25804,7 @@
       </c>
       <c r="N372" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O372" s="3" t="inlineStr"/>
@@ -25821,7 +25857,7 @@
       <c r="M373" s="3" t="inlineStr"/>
       <c r="N373" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O373" s="3" t="inlineStr"/>
@@ -25874,7 +25910,7 @@
       <c r="M374" s="3" t="inlineStr"/>
       <c r="N374" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O374" s="3" t="inlineStr"/>
@@ -25935,7 +25971,7 @@
       </c>
       <c r="N375" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O375" s="3" t="inlineStr"/>
@@ -26000,7 +26036,7 @@
       </c>
       <c r="N376" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O376" s="3" t="inlineStr"/>
@@ -26061,7 +26097,7 @@
       </c>
       <c r="N377" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O377" s="3" t="inlineStr"/>
@@ -26126,7 +26162,7 @@
       </c>
       <c r="N378" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O378" s="3" t="inlineStr"/>
@@ -26183,7 +26219,7 @@
       </c>
       <c r="N379" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O379" s="3" t="inlineStr"/>
@@ -26236,7 +26272,7 @@
       <c r="M380" s="3" t="inlineStr"/>
       <c r="N380" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O380" s="3" t="inlineStr"/>
@@ -26289,7 +26325,7 @@
       <c r="M381" s="3" t="inlineStr"/>
       <c r="N381" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O381" s="3" t="inlineStr"/>
@@ -26350,7 +26386,7 @@
       </c>
       <c r="N382" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O382" s="3" t="inlineStr"/>
@@ -26411,7 +26447,7 @@
       </c>
       <c r="N383" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O383" s="3" t="inlineStr"/>
@@ -26476,7 +26512,7 @@
       </c>
       <c r="N384" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O384" s="3" t="inlineStr"/>
@@ -26537,7 +26573,7 @@
       <c r="M385" s="3" t="inlineStr"/>
       <c r="N385" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O385" s="3" t="inlineStr"/>
@@ -26602,7 +26638,7 @@
       </c>
       <c r="N386" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O386" s="3" t="inlineStr"/>
@@ -26659,7 +26695,7 @@
       </c>
       <c r="N387" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O387" s="3" t="inlineStr"/>
@@ -26712,7 +26748,7 @@
       <c r="M388" s="3" t="inlineStr"/>
       <c r="N388" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O388" s="3" t="inlineStr"/>
@@ -26765,7 +26801,7 @@
       <c r="M389" s="3" t="inlineStr"/>
       <c r="N389" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O389" s="3" t="inlineStr"/>
@@ -26826,7 +26862,7 @@
       </c>
       <c r="N390" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O390" s="3" t="inlineStr"/>
@@ -26887,7 +26923,7 @@
       </c>
       <c r="N391" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O391" s="3" t="inlineStr"/>
@@ -26948,7 +26984,7 @@
       </c>
       <c r="N392" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O392" s="3" t="inlineStr"/>
@@ -27009,7 +27045,7 @@
       </c>
       <c r="N393" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O393" s="3" t="inlineStr"/>
@@ -27074,7 +27110,7 @@
       </c>
       <c r="N394" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O394" s="3" t="inlineStr"/>
@@ -27131,7 +27167,7 @@
       </c>
       <c r="N395" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O395" s="3" t="inlineStr">
@@ -27192,7 +27228,7 @@
       </c>
       <c r="N396" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O396" s="3" t="inlineStr"/>
@@ -27245,7 +27281,7 @@
       <c r="M397" s="3" t="inlineStr"/>
       <c r="N397" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O397" s="3" t="inlineStr"/>
@@ -27298,7 +27334,7 @@
       <c r="M398" s="3" t="inlineStr"/>
       <c r="N398" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O398" s="3" t="inlineStr"/>
@@ -27359,7 +27395,7 @@
       </c>
       <c r="N399" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O399" s="3" t="inlineStr"/>
@@ -27416,7 +27452,7 @@
       </c>
       <c r="N400" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O400" s="3" t="inlineStr"/>
@@ -27477,7 +27513,7 @@
       </c>
       <c r="N401" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O401" s="3" t="inlineStr"/>
@@ -27538,7 +27574,7 @@
       </c>
       <c r="N402" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O402" s="3" t="inlineStr"/>
@@ -27599,7 +27635,7 @@
       </c>
       <c r="N403" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O403" s="3" t="inlineStr"/>
@@ -27660,7 +27696,7 @@
       </c>
       <c r="N404" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O404" s="3" t="inlineStr"/>
@@ -27721,7 +27757,7 @@
       </c>
       <c r="N405" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O405" s="3" t="inlineStr"/>
@@ -27778,7 +27814,7 @@
       </c>
       <c r="N406" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O406" s="3" t="inlineStr"/>
@@ -27835,7 +27871,7 @@
       </c>
       <c r="N407" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O407" s="3" t="inlineStr"/>
@@ -27896,7 +27932,7 @@
       </c>
       <c r="N408" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O408" s="3" t="inlineStr"/>
@@ -27953,7 +27989,7 @@
       </c>
       <c r="N409" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O409" s="3" t="inlineStr"/>
@@ -28010,7 +28046,7 @@
       </c>
       <c r="N410" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O410" s="3" t="inlineStr"/>
@@ -28067,7 +28103,7 @@
       </c>
       <c r="N411" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O411" s="3" t="inlineStr"/>
@@ -28128,7 +28164,7 @@
       </c>
       <c r="N412" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O412" s="3" t="inlineStr"/>
@@ -28189,7 +28225,7 @@
       </c>
       <c r="N413" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O413" s="3" t="inlineStr"/>
@@ -28250,7 +28286,7 @@
       </c>
       <c r="N414" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O414" s="3" t="inlineStr"/>
@@ -28307,7 +28343,7 @@
       </c>
       <c r="N415" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O415" s="3" t="inlineStr"/>
@@ -28364,7 +28400,7 @@
       </c>
       <c r="N416" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O416" s="3" t="inlineStr">
@@ -28425,7 +28461,7 @@
       </c>
       <c r="N417" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O417" s="3" t="inlineStr"/>
@@ -28482,7 +28518,7 @@
       </c>
       <c r="N418" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O418" s="3" t="inlineStr"/>
@@ -28535,7 +28571,7 @@
       <c r="M419" s="3" t="inlineStr"/>
       <c r="N419" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O419" s="3" t="inlineStr"/>
@@ -28588,7 +28624,7 @@
       <c r="M420" s="3" t="inlineStr"/>
       <c r="N420" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O420" s="3" t="inlineStr"/>
@@ -28641,7 +28677,7 @@
       <c r="M421" s="3" t="inlineStr"/>
       <c r="N421" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O421" s="3" t="inlineStr"/>
@@ -28702,7 +28738,7 @@
       </c>
       <c r="N422" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O422" s="3" t="inlineStr"/>
@@ -28763,7 +28799,7 @@
       </c>
       <c r="N423" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O423" s="3" t="inlineStr"/>
@@ -28824,7 +28860,7 @@
       <c r="M424" s="3" t="inlineStr"/>
       <c r="N424" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O424" s="3" t="inlineStr"/>
@@ -28885,7 +28921,7 @@
       </c>
       <c r="N425" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O425" s="3" t="inlineStr"/>
@@ -28942,7 +28978,7 @@
       </c>
       <c r="N426" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O426" s="3" t="inlineStr"/>
@@ -28995,7 +29031,7 @@
       <c r="M427" s="3" t="inlineStr"/>
       <c r="N427" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O427" s="3" t="inlineStr"/>
@@ -29052,7 +29088,7 @@
       </c>
       <c r="N428" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O428" s="3" t="inlineStr"/>
@@ -29109,7 +29145,7 @@
       </c>
       <c r="N429" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O429" s="3" t="inlineStr"/>
@@ -29162,7 +29198,7 @@
       <c r="M430" s="3" t="inlineStr"/>
       <c r="N430" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O430" s="3" t="inlineStr"/>
@@ -29215,7 +29251,7 @@
       <c r="M431" s="3" t="inlineStr"/>
       <c r="N431" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O431" s="3" t="inlineStr"/>
@@ -29276,7 +29312,7 @@
       </c>
       <c r="N432" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O432" s="3" t="inlineStr"/>
@@ -29337,7 +29373,7 @@
       </c>
       <c r="N433" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O433" s="3" t="inlineStr"/>
@@ -29398,7 +29434,7 @@
       <c r="M434" s="3" t="inlineStr"/>
       <c r="N434" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O434" s="3" t="inlineStr"/>
@@ -29459,7 +29495,7 @@
       </c>
       <c r="N435" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O435" s="3" t="inlineStr"/>
@@ -29516,7 +29552,7 @@
       </c>
       <c r="N436" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O436" s="3" t="inlineStr">
@@ -29573,7 +29609,7 @@
       <c r="M437" s="3" t="inlineStr"/>
       <c r="N437" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O437" s="3" t="inlineStr"/>
@@ -29626,7 +29662,7 @@
       <c r="M438" s="3" t="inlineStr"/>
       <c r="N438" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O438" s="3" t="inlineStr"/>
@@ -29679,7 +29715,7 @@
       <c r="M439" s="3" t="inlineStr"/>
       <c r="N439" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O439" s="3" t="inlineStr"/>
@@ -29740,7 +29776,7 @@
       </c>
       <c r="N440" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O440" s="3" t="inlineStr"/>
@@ -29801,7 +29837,7 @@
       </c>
       <c r="N441" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O441" s="3" t="inlineStr">
@@ -29866,7 +29902,7 @@
       </c>
       <c r="N442" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O442" s="3" t="inlineStr"/>
@@ -29919,7 +29955,7 @@
       <c r="M443" s="3" t="inlineStr"/>
       <c r="N443" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O443" s="3" t="inlineStr"/>
@@ -29972,7 +30008,7 @@
       <c r="M444" s="3" t="inlineStr"/>
       <c r="N444" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O444" s="3" t="inlineStr"/>
@@ -30025,7 +30061,7 @@
       <c r="M445" s="3" t="inlineStr"/>
       <c r="N445" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O445" s="3" t="inlineStr"/>
@@ -30086,7 +30122,7 @@
       </c>
       <c r="N446" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O446" s="3" t="inlineStr"/>
@@ -30151,7 +30187,7 @@
       </c>
       <c r="N447" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O447" s="3" t="inlineStr"/>
@@ -30208,7 +30244,7 @@
       </c>
       <c r="N448" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O448" s="3" t="inlineStr"/>
@@ -30265,7 +30301,7 @@
       </c>
       <c r="N449" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O449" s="3" t="inlineStr">
@@ -30326,7 +30362,7 @@
       </c>
       <c r="N450" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O450" s="3" t="inlineStr"/>
@@ -30383,7 +30419,7 @@
       </c>
       <c r="N451" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O451" s="3" t="inlineStr"/>
@@ -30444,7 +30480,7 @@
       </c>
       <c r="N452" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O452" s="3" t="inlineStr"/>
@@ -30501,7 +30537,7 @@
       </c>
       <c r="N453" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O453" s="3" t="inlineStr"/>
@@ -30554,7 +30590,7 @@
       <c r="M454" s="3" t="inlineStr"/>
       <c r="N454" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O454" s="3" t="inlineStr"/>
@@ -30607,7 +30643,7 @@
       <c r="M455" s="3" t="inlineStr"/>
       <c r="N455" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O455" s="3" t="inlineStr"/>
@@ -30668,7 +30704,7 @@
       </c>
       <c r="N456" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O456" s="3" t="inlineStr"/>
@@ -30733,7 +30769,7 @@
       </c>
       <c r="N457" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O457" s="3" t="inlineStr"/>
@@ -30790,7 +30826,7 @@
       </c>
       <c r="N458" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O458" s="3" t="inlineStr"/>
@@ -30847,7 +30883,7 @@
       </c>
       <c r="N459" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O459" s="3" t="inlineStr"/>
@@ -30904,7 +30940,7 @@
       </c>
       <c r="N460" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O460" s="3" t="inlineStr"/>
@@ -30965,7 +31001,7 @@
       </c>
       <c r="N461" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O461" s="3" t="inlineStr"/>
@@ -31022,7 +31058,7 @@
       </c>
       <c r="N462" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O462" s="3" t="inlineStr"/>
@@ -31079,7 +31115,7 @@
       </c>
       <c r="N463" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O463" s="3" t="inlineStr"/>
@@ -31136,7 +31172,7 @@
       </c>
       <c r="N464" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O464" s="3" t="inlineStr"/>
@@ -31189,7 +31225,7 @@
       <c r="M465" s="3" t="inlineStr"/>
       <c r="N465" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O465" s="3" t="inlineStr"/>
@@ -31242,7 +31278,7 @@
       <c r="M466" s="3" t="inlineStr"/>
       <c r="N466" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O466" s="3" t="inlineStr"/>
@@ -31303,7 +31339,7 @@
       </c>
       <c r="N467" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O467" s="3" t="inlineStr"/>
@@ -31368,7 +31404,7 @@
       </c>
       <c r="N468" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O468" s="3" t="inlineStr"/>
@@ -31421,7 +31457,7 @@
       <c r="M469" s="3" t="inlineStr"/>
       <c r="N469" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O469" s="3" t="inlineStr"/>
@@ -31478,7 +31514,7 @@
       </c>
       <c r="N470" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O470" s="3" t="inlineStr"/>
@@ -31535,7 +31571,7 @@
       </c>
       <c r="N471" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O471" s="3" t="inlineStr"/>
@@ -31596,7 +31632,7 @@
       </c>
       <c r="N472" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O472" s="3" t="inlineStr"/>
@@ -31653,7 +31689,7 @@
       </c>
       <c r="N473" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O473" s="3" t="inlineStr"/>
@@ -31710,7 +31746,7 @@
       </c>
       <c r="N474" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O474" s="3" t="inlineStr"/>
@@ -31767,7 +31803,7 @@
       </c>
       <c r="N475" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O475" s="3" t="inlineStr"/>
@@ -31824,7 +31860,7 @@
       </c>
       <c r="N476" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O476" s="3" t="inlineStr"/>
@@ -31885,7 +31921,7 @@
       </c>
       <c r="N477" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O477" s="3" t="inlineStr"/>
@@ -31946,7 +31982,7 @@
       </c>
       <c r="N478" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O478" s="3" t="inlineStr"/>
@@ -32007,7 +32043,7 @@
       </c>
       <c r="N479" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O479" s="3" t="inlineStr"/>
@@ -32064,7 +32100,7 @@
       </c>
       <c r="N480" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O480" s="3" t="inlineStr"/>
@@ -32125,7 +32161,7 @@
       </c>
       <c r="N481" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O481" s="3" t="inlineStr"/>
@@ -32182,7 +32218,7 @@
       </c>
       <c r="N482" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O482" s="3" t="inlineStr"/>
@@ -32235,7 +32271,7 @@
       <c r="M483" s="3" t="inlineStr"/>
       <c r="N483" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O483" s="3" t="inlineStr"/>
@@ -32288,7 +32324,7 @@
       <c r="M484" s="3" t="inlineStr"/>
       <c r="N484" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O484" s="3" t="inlineStr"/>
@@ -32349,7 +32385,7 @@
       </c>
       <c r="N485" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O485" s="3" t="inlineStr"/>
@@ -32414,7 +32450,7 @@
       </c>
       <c r="N486" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O486" s="3" t="inlineStr"/>
@@ -32467,7 +32503,7 @@
       <c r="M487" s="3" t="inlineStr"/>
       <c r="N487" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O487" s="3" t="inlineStr"/>
@@ -32524,7 +32560,7 @@
       </c>
       <c r="N488" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O488" s="3" t="inlineStr"/>
@@ -32581,7 +32617,7 @@
       </c>
       <c r="N489" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O489" s="3" t="inlineStr"/>
@@ -32638,7 +32674,7 @@
       </c>
       <c r="N490" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O490" s="3" t="inlineStr"/>
@@ -32695,7 +32731,7 @@
       </c>
       <c r="N491" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O491" s="3" t="inlineStr"/>
@@ -32752,7 +32788,7 @@
       </c>
       <c r="N492" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O492" s="3" t="inlineStr"/>
@@ -32813,7 +32849,7 @@
       </c>
       <c r="N493" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O493" s="3" t="inlineStr"/>
@@ -32874,7 +32910,7 @@
       </c>
       <c r="N494" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O494" s="3" t="inlineStr"/>
@@ -32935,7 +32971,7 @@
       </c>
       <c r="N495" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O495" s="3" t="inlineStr"/>
@@ -32988,7 +33024,7 @@
       <c r="M496" s="3" t="inlineStr"/>
       <c r="N496" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O496" s="3" t="inlineStr"/>
@@ -33041,7 +33077,7 @@
       <c r="M497" s="3" t="inlineStr"/>
       <c r="N497" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O497" s="3" t="inlineStr"/>
@@ -33102,7 +33138,7 @@
       </c>
       <c r="N498" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O498" s="3" t="inlineStr"/>
@@ -33167,7 +33203,7 @@
       </c>
       <c r="N499" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O499" s="3" t="inlineStr"/>
@@ -33220,7 +33256,7 @@
       <c r="M500" s="3" t="inlineStr"/>
       <c r="N500" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O500" s="3" t="inlineStr"/>
@@ -33277,7 +33313,7 @@
       </c>
       <c r="N501" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O501" s="3" t="inlineStr"/>
@@ -33338,7 +33374,7 @@
       </c>
       <c r="N502" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O502" s="3" t="inlineStr"/>
@@ -33395,7 +33431,7 @@
       </c>
       <c r="N503" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O503" s="3" t="inlineStr"/>
@@ -33452,7 +33488,7 @@
       </c>
       <c r="N504" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O504" s="3" t="inlineStr"/>
@@ -33513,7 +33549,7 @@
       </c>
       <c r="N505" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O505" s="3" t="inlineStr"/>
@@ -33578,7 +33614,7 @@
       </c>
       <c r="N506" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O506" s="3" t="inlineStr"/>
@@ -33643,7 +33679,7 @@
       </c>
       <c r="N507" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O507" s="3" t="inlineStr"/>
@@ -33696,7 +33732,7 @@
       <c r="M508" s="3" t="inlineStr"/>
       <c r="N508" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O508" s="3" t="inlineStr"/>
@@ -33749,7 +33785,7 @@
       <c r="M509" s="3" t="inlineStr"/>
       <c r="N509" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O509" s="3" t="inlineStr"/>
@@ -33810,7 +33846,7 @@
       </c>
       <c r="N510" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O510" s="3" t="inlineStr"/>
@@ -33875,7 +33911,7 @@
       </c>
       <c r="N511" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O511" s="3" t="inlineStr">
@@ -33932,7 +33968,7 @@
       <c r="M512" s="3" t="inlineStr"/>
       <c r="N512" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O512" s="3" t="inlineStr"/>
@@ -33989,7 +34025,7 @@
       </c>
       <c r="N513" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O513" s="3" t="inlineStr"/>
@@ -34054,7 +34090,7 @@
       </c>
       <c r="N514" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O514" s="3" t="inlineStr">
@@ -34115,7 +34151,7 @@
       </c>
       <c r="N515" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O515" s="3" t="inlineStr"/>
@@ -34172,7 +34208,7 @@
       </c>
       <c r="N516" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O516" s="3" t="inlineStr"/>
@@ -34233,7 +34269,7 @@
       </c>
       <c r="N517" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O517" s="3" t="inlineStr"/>
@@ -34282,7 +34318,7 @@
       <c r="M518" s="3" t="inlineStr"/>
       <c r="N518" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O518" s="3" t="inlineStr"/>
@@ -34335,7 +34371,7 @@
       <c r="M519" s="3" t="inlineStr"/>
       <c r="N519" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O519" s="3" t="inlineStr"/>
@@ -34388,7 +34424,7 @@
       <c r="M520" s="3" t="inlineStr"/>
       <c r="N520" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O520" s="3" t="inlineStr"/>
@@ -34449,7 +34485,7 @@
       </c>
       <c r="N521" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O521" s="3" t="inlineStr"/>
@@ -34514,7 +34550,7 @@
       </c>
       <c r="N522" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O522" s="3" t="inlineStr"/>
@@ -34571,7 +34607,7 @@
       </c>
       <c r="N523" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O523" s="3" t="inlineStr"/>
@@ -34632,7 +34668,7 @@
       </c>
       <c r="N524" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O524" s="3" t="inlineStr"/>
@@ -34693,7 +34729,7 @@
       </c>
       <c r="N525" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O525" s="3" t="inlineStr"/>
@@ -34754,7 +34790,7 @@
       </c>
       <c r="N526" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O526" s="3" t="inlineStr"/>
@@ -34811,7 +34847,7 @@
       </c>
       <c r="N527" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O527" s="3" t="inlineStr"/>
@@ -34872,7 +34908,7 @@
       </c>
       <c r="N528" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O528" s="3" t="inlineStr"/>
@@ -34929,7 +34965,7 @@
       </c>
       <c r="N529" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O529" s="3" t="inlineStr">
@@ -34998,7 +35034,7 @@
       </c>
       <c r="N530" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O530" s="3" t="inlineStr"/>
@@ -35059,7 +35095,7 @@
       </c>
       <c r="N531" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O531" s="3" t="inlineStr"/>
@@ -35112,7 +35148,7 @@
       <c r="M532" s="3" t="inlineStr"/>
       <c r="N532" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O532" s="3" t="inlineStr"/>
@@ -35165,7 +35201,7 @@
       <c r="M533" s="3" t="inlineStr"/>
       <c r="N533" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O533" s="3" t="inlineStr"/>
@@ -35226,7 +35262,7 @@
       </c>
       <c r="N534" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O534" s="3" t="inlineStr"/>
@@ -35291,7 +35327,7 @@
       </c>
       <c r="N535" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O535" s="3" t="inlineStr">
@@ -35352,7 +35388,7 @@
       </c>
       <c r="N536" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O536" s="3" t="inlineStr"/>
@@ -35409,7 +35445,7 @@
       <c r="M537" s="3" t="inlineStr"/>
       <c r="N537" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O537" s="3" t="inlineStr"/>
@@ -35470,7 +35506,7 @@
       </c>
       <c r="N538" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O538" s="3" t="inlineStr"/>
@@ -35527,7 +35563,7 @@
       </c>
       <c r="N539" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O539" s="3" t="inlineStr"/>
@@ -35584,7 +35620,7 @@
       <c r="M540" s="3" t="inlineStr"/>
       <c r="N540" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O540" s="3" t="inlineStr"/>
@@ -35645,7 +35681,7 @@
       </c>
       <c r="N541" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O541" s="3" t="inlineStr"/>
@@ -35698,7 +35734,7 @@
       <c r="M542" s="3" t="inlineStr"/>
       <c r="N542" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O542" s="3" t="inlineStr"/>
@@ -35751,7 +35787,7 @@
       <c r="M543" s="3" t="inlineStr"/>
       <c r="N543" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O543" s="3" t="inlineStr"/>
@@ -35812,7 +35848,7 @@
       </c>
       <c r="N544" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O544" s="3" t="inlineStr"/>
@@ -35873,7 +35909,7 @@
       <c r="M545" s="3" t="inlineStr"/>
       <c r="N545" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O545" s="3" t="inlineStr"/>
@@ -35930,7 +35966,7 @@
       </c>
       <c r="N546" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O546" s="3" t="inlineStr"/>
@@ -35987,7 +36023,7 @@
       </c>
       <c r="N547" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O547" s="3" t="inlineStr"/>
@@ -36048,7 +36084,7 @@
       </c>
       <c r="N548" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O548" s="3" t="inlineStr"/>
@@ -36109,7 +36145,7 @@
       </c>
       <c r="N549" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O549" s="3" t="inlineStr"/>
@@ -36166,7 +36202,7 @@
       </c>
       <c r="N550" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O550" s="3" t="inlineStr"/>
@@ -36223,7 +36259,7 @@
       <c r="M551" s="3" t="inlineStr"/>
       <c r="N551" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O551" s="3" t="inlineStr"/>
@@ -36280,7 +36316,7 @@
       </c>
       <c r="N552" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O552" s="3" t="inlineStr"/>
@@ -36333,7 +36369,7 @@
       <c r="M553" s="3" t="inlineStr"/>
       <c r="N553" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O553" s="3" t="inlineStr"/>
@@ -36386,7 +36422,7 @@
       <c r="M554" s="3" t="inlineStr"/>
       <c r="N554" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O554" s="3" t="inlineStr"/>
@@ -36439,7 +36475,7 @@
       <c r="M555" s="3" t="inlineStr"/>
       <c r="N555" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O555" s="3" t="inlineStr"/>
@@ -36500,7 +36536,7 @@
       </c>
       <c r="N556" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O556" s="3" t="inlineStr"/>
@@ -36561,7 +36597,7 @@
       </c>
       <c r="N557" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O557" s="3" t="inlineStr"/>
@@ -36622,7 +36658,7 @@
       </c>
       <c r="N558" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O558" s="3" t="inlineStr"/>
@@ -36679,7 +36715,7 @@
       </c>
       <c r="N559" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O559" s="3" t="inlineStr"/>
@@ -36744,7 +36780,7 @@
       </c>
       <c r="N560" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O560" s="3" t="inlineStr"/>
@@ -36805,7 +36841,7 @@
       </c>
       <c r="N561" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O561" s="3" t="inlineStr"/>
@@ -36866,7 +36902,7 @@
       </c>
       <c r="N562" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O562" s="3" t="inlineStr"/>
@@ -36927,7 +36963,7 @@
       </c>
       <c r="N563" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O563" s="3" t="inlineStr"/>
@@ -36988,7 +37024,7 @@
       </c>
       <c r="N564" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O564" s="3" t="inlineStr"/>
@@ -37045,7 +37081,7 @@
       </c>
       <c r="N565" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O565" s="3" t="inlineStr"/>
@@ -37110,7 +37146,7 @@
       </c>
       <c r="N566" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O566" s="3" t="inlineStr"/>
@@ -37171,7 +37207,7 @@
       </c>
       <c r="N567" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O567" s="3" t="inlineStr"/>
@@ -37232,7 +37268,7 @@
       </c>
       <c r="N568" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O568" s="3" t="inlineStr"/>
@@ -37293,7 +37329,7 @@
       </c>
       <c r="N569" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O569" s="3" t="inlineStr"/>
@@ -37350,7 +37386,7 @@
       </c>
       <c r="N570" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O570" s="3" t="inlineStr"/>
@@ -37399,7 +37435,7 @@
       <c r="M571" s="3" t="inlineStr"/>
       <c r="N571" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O571" s="3" t="inlineStr"/>
@@ -37456,7 +37492,7 @@
       </c>
       <c r="N572" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O572" s="3" t="inlineStr"/>
@@ -37513,7 +37549,7 @@
       </c>
       <c r="N573" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O573" s="3" t="inlineStr"/>
@@ -37566,7 +37602,7 @@
       <c r="M574" s="3" t="inlineStr"/>
       <c r="N574" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O574" s="3" t="inlineStr"/>
@@ -37619,7 +37655,7 @@
       <c r="M575" s="3" t="inlineStr"/>
       <c r="N575" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O575" s="3" t="inlineStr"/>
@@ -37672,7 +37708,7 @@
       <c r="M576" s="3" t="inlineStr"/>
       <c r="N576" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O576" s="3" t="inlineStr"/>
@@ -37733,7 +37769,7 @@
       </c>
       <c r="N577" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O577" s="3" t="inlineStr"/>
@@ -37794,7 +37830,7 @@
       </c>
       <c r="N578" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O578" s="3" t="inlineStr"/>
@@ -37851,7 +37887,7 @@
       </c>
       <c r="N579" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O579" s="3" t="inlineStr"/>
@@ -37904,7 +37940,7 @@
       <c r="M580" s="3" t="inlineStr"/>
       <c r="N580" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O580" s="3" t="inlineStr"/>
@@ -37965,7 +38001,7 @@
       </c>
       <c r="N581" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O581" s="3" t="inlineStr"/>
@@ -38022,7 +38058,7 @@
       </c>
       <c r="N582" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O582" s="3" t="inlineStr"/>
@@ -38079,7 +38115,7 @@
       </c>
       <c r="N583" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O583" s="3" t="inlineStr"/>
@@ -38128,7 +38164,7 @@
       <c r="M584" s="3" t="inlineStr"/>
       <c r="N584" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O584" s="3" t="inlineStr">
@@ -38185,7 +38221,7 @@
       <c r="M585" s="3" t="inlineStr"/>
       <c r="N585" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O585" s="3" t="inlineStr"/>
@@ -38238,7 +38274,7 @@
       <c r="M586" s="3" t="inlineStr"/>
       <c r="N586" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O586" s="3" t="inlineStr"/>
@@ -38299,7 +38335,7 @@
       </c>
       <c r="N587" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O587" s="3" t="inlineStr"/>
@@ -38356,7 +38392,7 @@
       </c>
       <c r="N588" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O588" s="3" t="inlineStr"/>
@@ -38417,7 +38453,7 @@
       </c>
       <c r="N589" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O589" s="3" t="inlineStr"/>
@@ -38474,7 +38510,7 @@
       <c r="M590" s="3" t="inlineStr"/>
       <c r="N590" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O590" s="3" t="inlineStr">
@@ -38539,7 +38575,7 @@
       </c>
       <c r="N591" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O591" s="3" t="inlineStr"/>
@@ -38596,7 +38632,7 @@
       </c>
       <c r="N592" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O592" s="3" t="inlineStr"/>
@@ -38657,7 +38693,7 @@
       </c>
       <c r="N593" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O593" s="3" t="inlineStr"/>
@@ -38714,7 +38750,7 @@
       </c>
       <c r="N594" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O594" s="3" t="inlineStr">
@@ -38779,7 +38815,7 @@
       </c>
       <c r="N595" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O595" s="3" t="inlineStr"/>
@@ -38836,7 +38872,7 @@
       </c>
       <c r="N596" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O596" s="3" t="inlineStr"/>
@@ -38885,7 +38921,7 @@
       <c r="M597" s="3" t="inlineStr"/>
       <c r="N597" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O597" s="3" t="inlineStr"/>
@@ -38942,7 +38978,7 @@
       </c>
       <c r="N598" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O598" s="3" t="inlineStr"/>
@@ -39003,7 +39039,7 @@
       </c>
       <c r="N599" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O599" s="3" t="inlineStr"/>
@@ -39064,7 +39100,7 @@
       </c>
       <c r="N600" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O600" s="3" t="inlineStr"/>
@@ -39117,7 +39153,7 @@
       <c r="M601" s="3" t="inlineStr"/>
       <c r="N601" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O601" s="3" t="inlineStr"/>
@@ -39170,7 +39206,7 @@
       <c r="M602" s="3" t="inlineStr"/>
       <c r="N602" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O602" s="3" t="inlineStr"/>
@@ -39223,7 +39259,7 @@
       <c r="M603" s="3" t="inlineStr"/>
       <c r="N603" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O603" s="3" t="inlineStr"/>
@@ -39280,7 +39316,7 @@
       </c>
       <c r="N604" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O604" s="3" t="inlineStr"/>
@@ -39341,7 +39377,7 @@
       </c>
       <c r="N605" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O605" s="3" t="inlineStr"/>
@@ -39402,7 +39438,7 @@
       </c>
       <c r="N606" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O606" s="3" t="inlineStr"/>
@@ -39467,7 +39503,7 @@
       </c>
       <c r="N607" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O607" s="3" t="inlineStr"/>
@@ -39524,7 +39560,7 @@
       </c>
       <c r="N608" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O608" s="3" t="inlineStr"/>
@@ -39585,7 +39621,7 @@
       </c>
       <c r="N609" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O609" s="3" t="inlineStr"/>
@@ -39646,7 +39682,7 @@
       </c>
       <c r="N610" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O610" s="3" t="inlineStr"/>
@@ -39707,7 +39743,7 @@
       </c>
       <c r="N611" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O611" s="3" t="inlineStr"/>
@@ -39768,7 +39804,7 @@
       </c>
       <c r="N612" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O612" s="3" t="inlineStr"/>
@@ -39825,7 +39861,7 @@
       </c>
       <c r="N613" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O613" s="3" t="inlineStr"/>
@@ -39878,7 +39914,7 @@
       <c r="M614" s="3" t="inlineStr"/>
       <c r="N614" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O614" s="3" t="inlineStr"/>
@@ -39931,7 +39967,7 @@
       <c r="M615" s="3" t="inlineStr"/>
       <c r="N615" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O615" s="3" t="inlineStr"/>
@@ -39984,7 +40020,7 @@
       <c r="M616" s="3" t="inlineStr"/>
       <c r="N616" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O616" s="3" t="inlineStr"/>
@@ -40041,7 +40077,7 @@
       </c>
       <c r="N617" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O617" s="3" t="inlineStr"/>
@@ -40102,7 +40138,7 @@
       </c>
       <c r="N618" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O618" s="3" t="inlineStr"/>
@@ -40159,7 +40195,7 @@
       </c>
       <c r="N619" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O619" s="3" t="inlineStr"/>
@@ -40224,7 +40260,7 @@
       </c>
       <c r="N620" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O620" s="3" t="inlineStr"/>
@@ -40285,7 +40321,7 @@
       </c>
       <c r="N621" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O621" s="3" t="inlineStr"/>
@@ -40334,7 +40370,7 @@
       <c r="M622" s="3" t="inlineStr"/>
       <c r="N622" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O622" s="3" t="inlineStr">
@@ -40391,7 +40427,7 @@
       <c r="M623" s="3" t="inlineStr"/>
       <c r="N623" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O623" s="3" t="inlineStr"/>
@@ -40444,7 +40480,7 @@
       <c r="M624" s="3" t="inlineStr"/>
       <c r="N624" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O624" s="3" t="inlineStr"/>
@@ -40505,7 +40541,7 @@
       </c>
       <c r="N625" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O625" s="3" t="inlineStr"/>
@@ -40566,7 +40602,7 @@
       </c>
       <c r="N626" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O626" s="3" t="inlineStr"/>
@@ -40627,7 +40663,7 @@
       </c>
       <c r="N627" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O627" s="3" t="inlineStr"/>
@@ -40676,7 +40712,7 @@
       <c r="M628" s="3" t="inlineStr"/>
       <c r="N628" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O628" s="3" t="inlineStr">
@@ -40737,7 +40773,7 @@
       </c>
       <c r="N629" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O629" s="3" t="inlineStr"/>
@@ -40794,7 +40830,7 @@
       </c>
       <c r="N630" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O630" s="3" t="inlineStr"/>
@@ -40859,7 +40895,7 @@
       </c>
       <c r="N631" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O631" s="3" t="inlineStr"/>
@@ -40912,7 +40948,7 @@
       <c r="M632" s="3" t="inlineStr"/>
       <c r="N632" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O632" s="3" t="inlineStr"/>
@@ -40965,7 +41001,7 @@
       <c r="M633" s="3" t="inlineStr"/>
       <c r="N633" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O633" s="3" t="inlineStr"/>
@@ -41018,7 +41054,7 @@
       <c r="M634" s="3" t="inlineStr"/>
       <c r="N634" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O634" s="3" t="inlineStr"/>
@@ -41079,7 +41115,7 @@
       <c r="M635" s="3" t="inlineStr"/>
       <c r="N635" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O635" s="3" t="inlineStr"/>
@@ -41144,7 +41180,7 @@
       </c>
       <c r="N636" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O636" s="3" t="inlineStr"/>
@@ -41205,7 +41241,7 @@
       </c>
       <c r="N637" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O637" s="3" t="inlineStr"/>
@@ -41270,7 +41306,7 @@
       </c>
       <c r="N638" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O638" s="3" t="inlineStr"/>
@@ -41335,7 +41371,7 @@
       </c>
       <c r="N639" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O639" s="3" t="inlineStr"/>
@@ -41396,7 +41432,7 @@
       </c>
       <c r="N640" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O640" s="3" t="inlineStr"/>
@@ -41445,7 +41481,7 @@
       <c r="M641" s="3" t="inlineStr"/>
       <c r="N641" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O641" s="3" t="inlineStr"/>
@@ -41502,7 +41538,7 @@
       </c>
       <c r="N642" s="2" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="O642" s="3" t="inlineStr"/>

--- a/mapping/impix/S2_매핑정의서_IMPIX.xlsx
+++ b/mapping/impix/S2_매핑정의서_IMPIX.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 18:26 · tools/automap · 계획 mapping/impix/s2_plan.yaml</t>
+          <t>2026-10-30 13:51 · tools/automap · 계획 mapping/impix/s2_plan.yaml</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>EnterpriseID=const(IMPIX), SiteID=const(HQ), PlantID=xref(plant, plant_cd)</t>
+          <t>EnterpriseID=const(IMPIX), SiteID=const(HQ), PlantID=coalesce(xref(plant, plant_cd), const(P2))</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -1217,7 +1217,7 @@
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>EnterpriseID=const(IMPIX), SiteID=const(HQ), PlantID=xref(plant, plant_cd)</t>
+          <t>EnterpriseID=const(IMPIX), SiteID=const(HQ), PlantID=coalesce(xref(plant, plant_cd), const(P2))</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>plan_ver = (SELECT max(plan_ver) FROM erp.tb_pp_plan)</t>
+          <t>plan_ver = (SELECT max(v.plan_ver) FROM erp.tb_pp_plan v)</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -2824,7 +2824,7 @@
       <c r="G36" s="3" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>stk_dt = (SELECT max(stk_dt) FROM erp.tb_mm_stock_day)</t>
+          <t>stk_dt = (SELECT max(d.stk_dt) FROM erp.tb_mm_stock_day d)</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -5888,7 +5888,7 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>xref(plant, plant_cd)</t>
+          <t>coalesce(xref(plant, plant_cd), const(P2))</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -6230,7 +6230,7 @@
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>xref(plant, plant_cd)</t>
+          <t>coalesce(xref(plant, plant_cd), const(P2))</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -25326,7 +25326,7 @@
       <c r="K364" s="2" t="inlineStr"/>
       <c r="L364" s="3" t="inlineStr">
         <is>
-          <t>to_ts(to_date8(chk_dt) + '06:00')</t>
+          <t>to_ts(to_date8(chk_dt) + time '06:00')</t>
         </is>
       </c>
       <c r="M364" s="3" t="inlineStr">
